--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Long Term Bond Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Long Term Bond Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="73">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Long Term Bond Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,63 +64,84 @@
     <t>Government Securities</t>
   </si>
   <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>IN0020250018</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN0020240118</t>
+  </si>
+  <si>
+    <t>IN0020240142</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
+  </si>
+  <si>
+    <t>IN0020240126</t>
+  </si>
+  <si>
     <t>IN0020240019</t>
   </si>
   <si>
-    <t>SOV</t>
-  </si>
-  <si>
     <t>IN0020230077</t>
   </si>
   <si>
     <t>IN0020240134</t>
   </si>
   <si>
-    <t>IN0020240027</t>
-  </si>
-  <si>
-    <t>IN0020230085</t>
-  </si>
-  <si>
-    <t>IN0020240126</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>The Great Eastern Shipping Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE017A08268</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
     <t>HDFC Bank Ltd. **</t>
   </si>
   <si>
     <t>INE040A08666</t>
   </si>
   <si>
-    <t>CRISIL AAA</t>
-  </si>
-  <si>
-    <t>The Great Eastern Shipping Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE017A08268</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
     <t>LIC Housing Finance Ltd. **</t>
   </si>
   <si>
     <t>INE115A07QI4</t>
   </si>
   <si>
+    <t>INE115A07QV7</t>
+  </si>
+  <si>
+    <t>Jamnagar Utilities &amp; Power Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE936D07190</t>
+  </si>
+  <si>
     <t>INE115A07QR5</t>
   </si>
   <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A07QV7</t>
-  </si>
-  <si>
     <t>Indian Railway Finance Corporation Ltd. **</t>
   </si>
   <si>
@@ -202,7 +223,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -212,9 +233,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - CRISIL Long Duration Debt A-III Index</t>
   </si>
 </sst>
 </file>
@@ -588,13 +606,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -612,7 +630,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="13220700"/>
+          <a:off x="666750" y="14363700"/>
           <a:ext cx="3657600" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -627,13 +645,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -651,7 +669,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="16078200"/>
+          <a:off x="666750" y="17221200"/>
           <a:ext cx="3657600" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -985,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J81"/>
+  <dimension ref="B1:J86"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
@@ -1085,10 +1103,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>111846.09999999998</v>
+        <v>84065.90000000001</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9598598899352</v>
+        <v>0.6835367666059999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1122,10 +1140,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>111846.09999999998</v>
+        <v>84065.90000000001</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9598598899352</v>
+        <v>0.6835367666059999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1159,10 +1177,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>88686.76999999999</v>
+        <v>62040.33</v>
       </c>
       <c r="H9" s="10">
-        <v>0.761107211525</v>
+        <v>0.5044476603162</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1179,22 +1197,22 @@
         <v>16</v>
       </c>
       <c r="D10" s="14">
-        <v>7.10</v>
+        <v>7.34</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>29856200</v>
+        <v>37701500</v>
       </c>
       <c r="G10" s="16">
-        <v>30574.66</v>
+        <v>40130.76</v>
       </c>
       <c r="H10" s="17">
-        <v>0.2623908190131</v>
+        <v>0.3263017457956</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.98</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1202,28 +1220,28 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="14">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="15">
-        <v>22603830</v>
+        <v>4960700</v>
       </c>
       <c r="G11" s="16">
-        <v>23241.55</v>
+        <v>5127.57</v>
       </c>
       <c r="H11" s="17">
-        <v>0.1994582879952</v>
+        <v>0.0416920846425</v>
       </c>
       <c r="I11" s="16">
-        <v>6.96</v>
+        <v>6.83</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1234,25 +1252,25 @@
         <v>15</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
-        <v>6.92</v>
+        <v>6.90</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>18063500</v>
+        <v>5000000</v>
       </c>
       <c r="G12" s="16">
-        <v>18222.78</v>
+        <v>5033.66</v>
       </c>
       <c r="H12" s="17">
-        <v>0.1563873537399</v>
+        <v>0.0409285058578</v>
       </c>
       <c r="I12" s="16">
-        <v>6.94</v>
+        <v>6.97</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1260,28 +1278,28 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="14">
-        <v>7.23</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>7000000</v>
+        <v>4000000</v>
       </c>
       <c r="G13" s="16">
-        <v>7247.41</v>
+        <v>4151.02</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0621970561773</v>
+        <v>0.033751792212</v>
       </c>
       <c r="I13" s="16">
-        <v>6.95</v>
+        <v>6.82</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1292,25 +1310,25 @@
         <v>15</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="14">
-        <v>7.18</v>
+        <v>7.09</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>6237500</v>
+        <v>3500000</v>
       </c>
       <c r="G14" s="16">
-        <v>6408.06</v>
+        <v>3616.60</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0549937795444</v>
+        <v>0.0294064426849</v>
       </c>
       <c r="I14" s="16">
-        <v>6.87</v>
+        <v>6.94</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1321,25 +1339,25 @@
         <v>15</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="14">
-        <v>6.79</v>
+        <v>7.09</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="15">
-        <v>2972700</v>
+        <v>2500000</v>
       </c>
       <c r="G15" s="16">
-        <v>2992.31</v>
+        <v>2575.27</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0256799150551</v>
+        <v>0.0209394264373</v>
       </c>
       <c r="I15" s="16">
-        <v>6.81</v>
+        <v>6.99</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1347,36 +1365,57 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7.29</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="15">
+        <v>577700</v>
+      </c>
+      <c r="G16" s="16">
+        <v>603.04</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.0049032962441</v>
+      </c>
+      <c r="I16" s="16">
+        <v>6.88</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="9">
-        <v>23159.33</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0.1987526784102</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>13</v>
+      <c r="B17" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="14">
+        <v>6.79</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="15">
+        <v>381300</v>
+      </c>
+      <c r="G17" s="16">
+        <v>395</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0.0032117305924</v>
+      </c>
+      <c r="I17" s="16">
+        <v>6.37</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1384,28 +1423,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="14">
-        <v>7.80</v>
+        <v>7.10</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F18" s="15">
-        <v>7500</v>
+        <v>218500</v>
       </c>
       <c r="G18" s="16">
-        <v>7669.65</v>
+        <v>230.34</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0658207072472</v>
+        <v>0.0018728861383</v>
       </c>
       <c r="I18" s="16">
-        <v>7.42</v>
+        <v>6.39</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1413,28 +1452,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="14">
-        <v>8.24</v>
+        <v>7.18</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F19" s="15">
-        <v>536</v>
+        <v>103830</v>
       </c>
       <c r="G19" s="16">
-        <v>5324.68</v>
+        <v>110.58</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0456962447393</v>
+        <v>0.0008991219466</v>
       </c>
       <c r="I19" s="16">
-        <v>8.62</v>
+        <v>6.50</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1442,28 +1481,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D20" s="14">
-        <v>7.71</v>
+        <v>6.92</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F20" s="15">
-        <v>500</v>
+        <v>63500</v>
       </c>
       <c r="G20" s="16">
-        <v>5048.17</v>
+        <v>66.49</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0433232441772</v>
+        <v>0.0005406277647</v>
       </c>
       <c r="I20" s="16">
-        <v>7.54</v>
+        <v>6.52</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1471,57 +1510,36 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="15" customHeight="1">
+      <c r="B22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="14">
-        <v>7.68</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="15">
-        <v>2500</v>
-      </c>
-      <c r="G21" s="16">
-        <v>2527.90</v>
-      </c>
-      <c r="H21" s="17">
-        <v>0.0216943623047</v>
-      </c>
-      <c r="I21" s="16">
-        <v>7.50</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="15" customHeight="1">
-      <c r="B22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="14">
-        <v>7.61</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2500</v>
-      </c>
-      <c r="G22" s="16">
-        <v>2516.64</v>
-      </c>
-      <c r="H22" s="17">
-        <v>0.0215977293209</v>
-      </c>
-      <c r="I22" s="16">
-        <v>7.50</v>
+      <c r="C22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="9">
+        <v>22025.57</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0.17908910628980002</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1529,28 +1547,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D23" s="14">
-        <v>8.75</v>
+        <v>8.24</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>536</v>
       </c>
       <c r="G23" s="16">
-        <v>61.38</v>
+        <v>5406.73</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0005267613268</v>
+        <v>0.0439619244202</v>
       </c>
       <c r="I23" s="16">
-        <v>7.51</v>
+        <v>7.53</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -1558,28 +1576,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>8.620000000000001</v>
+        <v>7.80</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F24" s="15">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="G24" s="16">
-        <v>10.91</v>
+        <v>5228.48</v>
       </c>
       <c r="H24" s="17">
-        <v>0.0000936292941</v>
+        <v>0.0425125801718</v>
       </c>
       <c r="I24" s="16">
-        <v>7.22</v>
+        <v>7.03</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -1587,36 +1605,57 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="14">
+        <v>7.71</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="15">
+        <v>500</v>
+      </c>
+      <c r="G25" s="16">
+        <v>5170.51</v>
+      </c>
+      <c r="H25" s="17">
+        <v>0.0420412282163</v>
+      </c>
+      <c r="I25" s="16">
+        <v>7.13</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
-      <c r="B26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>13</v>
+      <c r="B26" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="14">
+        <v>7.61</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G26" s="16">
+        <v>2576.36</v>
+      </c>
+      <c r="H26" s="17">
+        <v>0.0209482891875</v>
+      </c>
+      <c r="I26" s="16">
+        <v>7.14</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -1624,36 +1663,57 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>7.43</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2500</v>
+      </c>
+      <c r="G27" s="16">
+        <v>2535.50</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0.0206160580179</v>
+      </c>
+      <c r="I27" s="16">
+        <v>7.21</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>13</v>
+      <c r="D28" s="14">
+        <v>7.68</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G28" s="16">
+        <v>1034.93</v>
+      </c>
+      <c r="H28" s="17">
+        <v>0.008414978081</v>
+      </c>
+      <c r="I28" s="16">
+        <v>7.14</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -1661,36 +1721,57 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="14">
+        <v>8.75</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="15">
+        <v>6</v>
+      </c>
+      <c r="G29" s="16">
+        <v>61.93</v>
+      </c>
+      <c r="H29" s="17">
+        <v>0.0005035505711</v>
+      </c>
+      <c r="I29" s="16">
+        <v>6.55</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
-      <c r="B30" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>13</v>
+      <c r="B30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="14">
+        <v>8.620000000000001</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="15">
+        <v>1</v>
+      </c>
+      <c r="G30" s="16">
+        <v>11.13</v>
+      </c>
+      <c r="H30" s="17">
+        <v>0.000090497624</v>
+      </c>
+      <c r="I30" s="16">
+        <v>6.86</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -1706,7 +1787,7 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>13</v>
@@ -1721,10 +1802,10 @@
         <v>13</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>13</v>
@@ -1743,7 +1824,7 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>13</v>
@@ -1758,10 +1839,10 @@
         <v>13</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>13</v>
@@ -1780,7 +1861,7 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>13</v>
@@ -1795,10 +1876,10 @@
         <v>13</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>13</v>
@@ -1817,7 +1898,7 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>13</v>
@@ -1832,10 +1913,10 @@
         <v>13</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>13</v>
@@ -1854,25 +1935,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="H40" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>13</v>
@@ -1891,7 +1972,7 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>13</v>
@@ -1906,10 +1987,10 @@
         <v>13</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>13</v>
@@ -1928,7 +2009,7 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>13</v>
@@ -1943,10 +2024,10 @@
         <v>13</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>13</v>
@@ -1965,7 +2046,7 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>13</v>
@@ -1980,10 +2061,10 @@
         <v>13</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I46" s="9" t="s">
         <v>13</v>
@@ -2002,7 +2083,7 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>13</v>
@@ -2016,11 +2097,11 @@
       <c r="F48" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="9">
-        <v>276.20</v>
-      </c>
-      <c r="H48" s="10">
-        <v>0.0023703401513</v>
+      <c r="G48" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>13</v>
@@ -2031,229 +2112,335 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="F49" s="15">
+        <v>13</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="15" customHeight="1">
+      <c r="B50" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="15" customHeight="1">
+      <c r="B51" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" customHeight="1">
+      <c r="B52" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="15" customHeight="1">
+      <c r="B53" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15" customHeight="1">
+      <c r="B54" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="9">
+        <v>283.29</v>
+      </c>
+      <c r="H54" s="10">
+        <v>0.002303420657</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15" customHeight="1">
+      <c r="B55" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="15">
         <v>2531.458</v>
       </c>
-      <c r="G49" s="16">
-        <v>276.20</v>
-      </c>
-      <c r="H49" s="17">
-        <v>0.0023703401513</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="9">
-        <v>1825.68</v>
-      </c>
-      <c r="H51" s="10">
-        <v>0.0156679312363</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="19">
-        <v>2575.3805161400232</v>
-      </c>
-      <c r="H53" s="20">
-        <v>0.02210183867623093</v>
-      </c>
-      <c r="I53" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J53" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="19">
-        <v>116523.36051614</v>
-      </c>
-      <c r="H54" s="20">
-        <v>0.9999999999990309</v>
-      </c>
-      <c r="I54" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" ht="15" customHeight="1">
-      <c r="B57" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-    </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
-      <c r="B58" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-    </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
-      <c r="B59" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-    </row>
-    <row r="60" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B60" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-    </row>
-    <row r="61" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B61" s="23" t="s">
+      <c r="G55" s="16">
+        <v>283.29</v>
+      </c>
+      <c r="H55" s="17">
+        <v>0.002303420657</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15" customHeight="1">
+      <c r="B56" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15" customHeight="1">
+      <c r="B57" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-    </row>
-    <row r="62" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B62" s="23" t="s">
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9">
+        <v>37308.94</v>
+      </c>
+      <c r="H57" s="10">
+        <v>0.3033576303011</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-    </row>
-    <row r="65" ht="15">
-      <c r="B65" s="22" t="s">
+      <c r="C59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="19">
+        <v>1328.5242765400035</v>
+      </c>
+      <c r="H59" s="20">
+        <v>0.01080218243479303</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="80" ht="15">
-      <c r="B80" s="22" t="s">
+      <c r="C60" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="19">
+        <v>122986.65427654</v>
+      </c>
+      <c r="H60" s="20">
+        <v>0.999999999998893</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" ht="15" customHeight="1">
+      <c r="B63" s="13" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="81" ht="15">
-      <c r="B81" s="22" t="s">
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+    </row>
+    <row r="64" spans="2:8" ht="15" customHeight="1">
+      <c r="B64" s="13" t="s">
         <v>66</v>
+      </c>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+    </row>
+    <row r="65" spans="2:8" ht="15" customHeight="1">
+      <c r="B65" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+    </row>
+    <row r="66" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B66" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+    </row>
+    <row r="67" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B67" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+    </row>
+    <row r="68" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B68" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+    </row>
+    <row r="71" ht="15">
+      <c r="B71" s="22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" ht="15">
+      <c r="B86" s="22" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B66:H66"/>
+    <mergeCell ref="B67:H67"/>
+    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B64:H64"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
